--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/14.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/14.xlsx
@@ -426,13 +426,13 @@
         <v>-7.030286368257936</v>
       </c>
       <c r="E2">
-        <v>-5.63637177882852</v>
+        <v>-2.820983260467798</v>
       </c>
       <c r="F2">
-        <v>-6.278511058494323</v>
+        <v>-5.911134671373458</v>
       </c>
       <c r="G2">
-        <v>-7.735097424266541</v>
+        <v>-8.425174020836542</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.121394016381506</v>
       </c>
       <c r="E3">
-        <v>-5.855658604175949</v>
+        <v>-3.730590663544496</v>
       </c>
       <c r="F3">
-        <v>-6.366937207824663</v>
+        <v>-5.868549131562938</v>
       </c>
       <c r="G3">
-        <v>-8.208651100386049</v>
+        <v>-8.22472710952475</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.435615244957535</v>
       </c>
       <c r="E4">
-        <v>-6.05130679520334</v>
+        <v>-3.730672176076634</v>
       </c>
       <c r="F4">
-        <v>-6.082029351673205</v>
+        <v>-6.045783307596309</v>
       </c>
       <c r="G4">
-        <v>-6.896268084980468</v>
+        <v>-8.40546634324126</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.74616884491561</v>
       </c>
       <c r="E5">
-        <v>-6.144584302813334</v>
+        <v>-4.717010042739299</v>
       </c>
       <c r="F5">
-        <v>-5.975920457579004</v>
+        <v>-5.682182204913702</v>
       </c>
       <c r="G5">
-        <v>-7.605903384596483</v>
+        <v>-7.887687089262629</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.99767788363169</v>
       </c>
       <c r="E6">
-        <v>-7.24477253450284</v>
+        <v>-5.491220601460662</v>
       </c>
       <c r="F6">
-        <v>-6.08250731966462</v>
+        <v>-5.511713305458995</v>
       </c>
       <c r="G6">
-        <v>-7.514423079709802</v>
+        <v>-8.319643760681194</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.06720832828931</v>
       </c>
       <c r="E7">
-        <v>-7.999728021743588</v>
+        <v>-6.627206420180802</v>
       </c>
       <c r="F7">
-        <v>-6.019915878709089</v>
+        <v>-5.431167001047785</v>
       </c>
       <c r="G7">
-        <v>-7.782001233466935</v>
+        <v>-8.21727507151585</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.87029212786469</v>
       </c>
       <c r="E8">
-        <v>-10.33085058667206</v>
+        <v>-7.057900526102315</v>
       </c>
       <c r="F8">
-        <v>-5.813026978022898</v>
+        <v>-5.741946427923478</v>
       </c>
       <c r="G8">
-        <v>-8.806082080039545</v>
+        <v>-7.944678130721182</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.31304054791735</v>
       </c>
       <c r="E9">
-        <v>-9.735360783137413</v>
+        <v>-7.685329656813058</v>
       </c>
       <c r="F9">
-        <v>-6.017337999351577</v>
+        <v>-5.479681166360141</v>
       </c>
       <c r="G9">
-        <v>-7.560479389252143</v>
+        <v>-7.361760582711851</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.33857239835716</v>
       </c>
       <c r="E10">
-        <v>-10.90309120465132</v>
+        <v>-8.121915307418549</v>
       </c>
       <c r="F10">
-        <v>-5.741250599305127</v>
+        <v>-5.591169478368121</v>
       </c>
       <c r="G10">
-        <v>-7.19637234866094</v>
+        <v>-7.307884764605752</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.90941106589716</v>
       </c>
       <c r="E11">
-        <v>-10.72450177521083</v>
+        <v>-9.376266379751177</v>
       </c>
       <c r="F11">
-        <v>-5.468771567665272</v>
+        <v>-5.272711914035879</v>
       </c>
       <c r="G11">
-        <v>-6.609756921284244</v>
+        <v>-7.248947122370106</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.02786677498009</v>
       </c>
       <c r="E12">
-        <v>-11.38850286200752</v>
+        <v>-9.964220802537058</v>
       </c>
       <c r="F12">
-        <v>-5.555001300827088</v>
+        <v>-5.063391755022471</v>
       </c>
       <c r="G12">
-        <v>-5.664857702919922</v>
+        <v>-6.556331337371485</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.7245894173446</v>
       </c>
       <c r="E13">
-        <v>-11.95795393999806</v>
+        <v>-10.30221251704755</v>
       </c>
       <c r="F13">
-        <v>-5.363160522380154</v>
+        <v>-4.901059080198061</v>
       </c>
       <c r="G13">
-        <v>-6.357731710470606</v>
+        <v>-6.150832545902775</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.06749338873496</v>
       </c>
       <c r="E14">
-        <v>-13.2450821071982</v>
+        <v>-11.49840892617367</v>
       </c>
       <c r="F14">
-        <v>-5.123490638462979</v>
+        <v>-5.087536179711869</v>
       </c>
       <c r="G14">
-        <v>-5.543648699090586</v>
+        <v>-5.464384307243816</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.148950462884768</v>
       </c>
       <c r="E15">
-        <v>-13.41894380977469</v>
+        <v>-12.12241453053462</v>
       </c>
       <c r="F15">
-        <v>-5.297979604923472</v>
+        <v>-4.785002321963642</v>
       </c>
       <c r="G15">
-        <v>-5.101780254327443</v>
+        <v>-5.201629618337401</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.080480785815098</v>
       </c>
       <c r="E16">
-        <v>-13.83148779187346</v>
+        <v>-12.99002939413819</v>
       </c>
       <c r="F16">
-        <v>-4.925882766157754</v>
+        <v>-4.455130683188226</v>
       </c>
       <c r="G16">
-        <v>-5.226501746973946</v>
+        <v>-4.607499252586559</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.978448074262337</v>
       </c>
       <c r="E17">
-        <v>-15.17752687743939</v>
+        <v>-13.71025148574011</v>
       </c>
       <c r="F17">
-        <v>-4.900930683250627</v>
+        <v>-4.52565622712777</v>
       </c>
       <c r="G17">
-        <v>-3.863325031359327</v>
+        <v>-4.098870346478472</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.957958152326836</v>
       </c>
       <c r="E18">
-        <v>-16.4055992151055</v>
+        <v>-14.99575845924551</v>
       </c>
       <c r="F18">
-        <v>-4.51641247527993</v>
+        <v>-4.024806242944925</v>
       </c>
       <c r="G18">
-        <v>-4.027984945391598</v>
+        <v>-3.479086563343817</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.1269956031862568</v>
       </c>
       <c r="E19">
-        <v>-18.06596421001784</v>
+        <v>-15.35746579213417</v>
       </c>
       <c r="F19">
-        <v>-4.231709225876963</v>
+        <v>-3.855410907644245</v>
       </c>
       <c r="G19">
-        <v>-3.017848116630398</v>
+        <v>-3.77569158038928</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.425206045526205</v>
       </c>
       <c r="E20">
-        <v>-17.61585653602545</v>
+        <v>-16.22035745734774</v>
       </c>
       <c r="F20">
-        <v>-3.991041159239414</v>
+        <v>-3.661210938834138</v>
       </c>
       <c r="G20">
-        <v>-3.711731840570561</v>
+        <v>-3.969057234792571</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.63260039378621</v>
       </c>
       <c r="E21">
-        <v>-18.967578856471</v>
+        <v>-16.80404152914439</v>
       </c>
       <c r="F21">
-        <v>-3.807590914215435</v>
+        <v>-3.717768551627676</v>
       </c>
       <c r="G21">
-        <v>-3.608343503379121</v>
+        <v>-3.164064981463389</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.459516786878759</v>
       </c>
       <c r="E22">
-        <v>-19.00679544137743</v>
+        <v>-16.88248828437926</v>
       </c>
       <c r="F22">
-        <v>-3.816957264438889</v>
+        <v>-3.350588073397573</v>
       </c>
       <c r="G22">
-        <v>-3.496172288871996</v>
+        <v>-3.371248852947597</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.893574427925179</v>
       </c>
       <c r="E23">
-        <v>-18.50911614793445</v>
+        <v>-17.63969895167583</v>
       </c>
       <c r="F23">
-        <v>-3.366479473652879</v>
+        <v>-3.210100275352388</v>
       </c>
       <c r="G23">
-        <v>-2.987169291117972</v>
+        <v>-3.035774720725552</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.950752681002255</v>
       </c>
       <c r="E24">
-        <v>-19.87914708879302</v>
+        <v>-18.29067614722646</v>
       </c>
       <c r="F24">
-        <v>-3.346976391521367</v>
+        <v>-2.718899114677352</v>
       </c>
       <c r="G24">
-        <v>-3.87367048616955</v>
+        <v>-2.986030463452463</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.671046390658331</v>
       </c>
       <c r="E25">
-        <v>-20.01087134072814</v>
+        <v>-18.83976720607851</v>
       </c>
       <c r="F25">
-        <v>-2.700432320166742</v>
+        <v>-3.010978975802249</v>
       </c>
       <c r="G25">
-        <v>-3.325546771777959</v>
+        <v>-3.186513790765187</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.106492057655394</v>
       </c>
       <c r="E26">
-        <v>-21.25268306853352</v>
+        <v>-18.41799872242612</v>
       </c>
       <c r="F26">
-        <v>-2.767689954702242</v>
+        <v>-2.745911347315241</v>
       </c>
       <c r="G26">
-        <v>-3.48220840778735</v>
+        <v>-3.936911837606247</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.316596384999653</v>
       </c>
       <c r="E27">
-        <v>-20.55221418055307</v>
+        <v>-18.45511862386699</v>
       </c>
       <c r="F27">
-        <v>-3.184001731959787</v>
+        <v>-2.893070816422573</v>
       </c>
       <c r="G27">
-        <v>-3.948419293900754</v>
+        <v>-3.489488297428207</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.361034716435177</v>
       </c>
       <c r="E28">
-        <v>-20.98255506550198</v>
+        <v>-18.75954528903263</v>
       </c>
       <c r="F28">
-        <v>-2.906419128751284</v>
+        <v>-2.716096747753681</v>
       </c>
       <c r="G28">
-        <v>-4.677586812198468</v>
+        <v>-4.208939364568161</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.2987974483709167</v>
       </c>
       <c r="E29">
-        <v>-21.24368951915429</v>
+        <v>-17.94486828657873</v>
       </c>
       <c r="F29">
-        <v>-2.917130747636884</v>
+        <v>-2.837860129025986</v>
       </c>
       <c r="G29">
-        <v>-3.556722166785266</v>
+        <v>-3.804903834227809</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.8174571758639608</v>
       </c>
       <c r="E30">
-        <v>-20.75113192981399</v>
+        <v>-17.58597313604883</v>
       </c>
       <c r="F30">
-        <v>-2.966339913200189</v>
+        <v>-2.705286553147147</v>
       </c>
       <c r="G30">
-        <v>-4.898509447670652</v>
+        <v>-4.258465125835658</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.943423784246115</v>
       </c>
       <c r="E31">
-        <v>-20.17506022282424</v>
+        <v>-18.09064892183365</v>
       </c>
       <c r="F31">
-        <v>-2.717707093984723</v>
+        <v>-3.067198614695446</v>
       </c>
       <c r="G31">
-        <v>-4.8323382634317</v>
+        <v>-3.889670352760847</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.037446484725586</v>
       </c>
       <c r="E32">
-        <v>-19.48217200033262</v>
+        <v>-18.09564382866411</v>
       </c>
       <c r="F32">
-        <v>-3.188797979221996</v>
+        <v>-3.010516746791486</v>
       </c>
       <c r="G32">
-        <v>-4.570735644372951</v>
+        <v>-3.794694111784696</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.059422242917124</v>
       </c>
       <c r="E33">
-        <v>-19.80953538634711</v>
+        <v>-17.90408937813966</v>
       </c>
       <c r="F33">
-        <v>-2.823141697013044</v>
+        <v>-2.870376863055478</v>
       </c>
       <c r="G33">
-        <v>-3.618900833103857</v>
+        <v>-4.169480972285587</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.970083300762933</v>
       </c>
       <c r="E34">
-        <v>-19.03861702822933</v>
+        <v>-17.05183056989609</v>
       </c>
       <c r="F34">
-        <v>-3.344053082956888</v>
+        <v>-3.021067662400944</v>
       </c>
       <c r="G34">
-        <v>-5.009561697785505</v>
+        <v>-3.285148184562233</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.734441860726737</v>
       </c>
       <c r="E35">
-        <v>-18.78504965464383</v>
+        <v>-17.0337710155535</v>
       </c>
       <c r="F35">
-        <v>-3.052862888422597</v>
+        <v>-2.714884017875982</v>
       </c>
       <c r="G35">
-        <v>-4.076891634643251</v>
+        <v>-4.433136129578684</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.324053616564574</v>
       </c>
       <c r="E36">
-        <v>-16.58444223909043</v>
+        <v>-16.3284340180148</v>
       </c>
       <c r="F36">
-        <v>-2.716333660830881</v>
+        <v>-3.020542477467569</v>
       </c>
       <c r="G36">
-        <v>-3.769623350415796</v>
+        <v>-4.065063055431435</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.717413916073851</v>
       </c>
       <c r="E37">
-        <v>-18.22117312815674</v>
+        <v>-15.76430842545728</v>
       </c>
       <c r="F37">
-        <v>-3.391178076134749</v>
+        <v>-2.852829556361975</v>
       </c>
       <c r="G37">
-        <v>-4.214222995248837</v>
+        <v>-3.665980101217833</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.904752156910799</v>
       </c>
       <c r="E38">
-        <v>-16.10311526528915</v>
+        <v>-15.10185154829721</v>
       </c>
       <c r="F38">
-        <v>-3.273731317398432</v>
+        <v>-3.227490192239358</v>
       </c>
       <c r="G38">
-        <v>-3.392350270214912</v>
+        <v>-3.866274727434818</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.887067520218062</v>
       </c>
       <c r="E39">
-        <v>-17.64710300667837</v>
+        <v>-14.59551381255157</v>
       </c>
       <c r="F39">
-        <v>-2.738770820303109</v>
+        <v>-2.998237028412387</v>
       </c>
       <c r="G39">
-        <v>-4.015861727626787</v>
+        <v>-3.239124980475284</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.67482938548689</v>
       </c>
       <c r="E40">
-        <v>-16.8913686219083</v>
+        <v>-14.53931545011638</v>
       </c>
       <c r="F40">
-        <v>-2.956520446007404</v>
+        <v>-3.275747563656846</v>
       </c>
       <c r="G40">
-        <v>-2.852350634576692</v>
+        <v>-3.463278708393797</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.284779553621719</v>
       </c>
       <c r="E41">
-        <v>-16.35034277526391</v>
+        <v>-13.89384487895908</v>
       </c>
       <c r="F41">
-        <v>-2.933346867914087</v>
+        <v>-3.026631806245548</v>
       </c>
       <c r="G41">
-        <v>-3.510242107413898</v>
+        <v>-3.156192504171002</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.740236342793645</v>
       </c>
       <c r="E42">
-        <v>-16.30191527422588</v>
+        <v>-12.52700651227592</v>
       </c>
       <c r="F42">
-        <v>-3.128924411715051</v>
+        <v>-2.994433165298731</v>
       </c>
       <c r="G42">
-        <v>-3.496728460522593</v>
+        <v>-3.251377309516127</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.070480838333764</v>
       </c>
       <c r="E43">
-        <v>-14.03077687600302</v>
+        <v>-12.8416131870108</v>
       </c>
       <c r="F43">
-        <v>-2.922025570620026</v>
+        <v>-3.371602097671791</v>
       </c>
       <c r="G43">
-        <v>-3.841587989348473</v>
+        <v>-3.244282810425469</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.31206318390015</v>
       </c>
       <c r="E44">
-        <v>-14.59703990829215</v>
+        <v>-12.04347870010692</v>
       </c>
       <c r="F44">
-        <v>-3.440184291684368</v>
+        <v>-3.366075230360313</v>
       </c>
       <c r="G44">
-        <v>-2.945492833324087</v>
+        <v>-3.01788453263133</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.509010929591258</v>
       </c>
       <c r="E45">
-        <v>-13.93182519046141</v>
+        <v>-11.78209065191018</v>
       </c>
       <c r="F45">
-        <v>-3.43544768687516</v>
+        <v>-3.342777397156577</v>
       </c>
       <c r="G45">
-        <v>-3.738474427436793</v>
+        <v>-3.035278138894661</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.715898653047112</v>
       </c>
       <c r="E46">
-        <v>-13.52447536804944</v>
+        <v>-11.30129803804181</v>
       </c>
       <c r="F46">
-        <v>-3.844565921606794</v>
+        <v>-3.541472087494275</v>
       </c>
       <c r="G46">
-        <v>-2.794369740001897</v>
+        <v>-2.53539569410133</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.993488560867536</v>
       </c>
       <c r="E47">
-        <v>-14.06375322372687</v>
+        <v>-11.38259320342751</v>
       </c>
       <c r="F47">
-        <v>-3.294644280849508</v>
+        <v>-3.499301559752557</v>
       </c>
       <c r="G47">
-        <v>-3.033086557747664</v>
+        <v>-3.050089519637361</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.401805274326924</v>
       </c>
       <c r="E48">
-        <v>-13.16546247719534</v>
+        <v>-10.72848230386357</v>
       </c>
       <c r="F48">
-        <v>-3.925271272559341</v>
+        <v>-3.69960162611688</v>
       </c>
       <c r="G48">
-        <v>-3.321567496039755</v>
+        <v>-3.483420067454723</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.9952946620400874</v>
       </c>
       <c r="E49">
-        <v>-10.75314890178335</v>
+        <v>-10.80359157375479</v>
       </c>
       <c r="F49">
-        <v>-3.604281389076741</v>
+        <v>-3.58995643158013</v>
       </c>
       <c r="G49">
-        <v>-3.566130737207875</v>
+        <v>-2.926745213935194</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.8116147190146563</v>
       </c>
       <c r="E50">
-        <v>-10.77572334471159</v>
+        <v>-9.641168523777869</v>
       </c>
       <c r="F50">
-        <v>-3.55042756748594</v>
+        <v>-3.930793169666403</v>
       </c>
       <c r="G50">
-        <v>-3.787722102878991</v>
+        <v>-3.259441798449791</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8707593580416209</v>
       </c>
       <c r="E51">
-        <v>-11.17875300292024</v>
+        <v>-8.972285742000912</v>
       </c>
       <c r="F51">
-        <v>-3.330230944473775</v>
+        <v>-4.057038018587853</v>
       </c>
       <c r="G51">
-        <v>-3.787741966152227</v>
+        <v>-2.861289107532725</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.169764674799658</v>
       </c>
       <c r="E52">
-        <v>-10.88491390998453</v>
+        <v>-8.926104364070689</v>
       </c>
       <c r="F52">
-        <v>-3.894702858661234</v>
+        <v>-3.952686920122394</v>
       </c>
       <c r="G52">
-        <v>-3.469476049643313</v>
+        <v>-3.163813380002404</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.685349992824746</v>
       </c>
       <c r="E53">
-        <v>-10.27781309909422</v>
+        <v>-8.315086423163743</v>
       </c>
       <c r="F53">
-        <v>-4.179563497870734</v>
+        <v>-4.042158054931366</v>
       </c>
       <c r="G53">
-        <v>-3.574625597061644</v>
+        <v>-2.543198649937392</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.376621130817995</v>
       </c>
       <c r="E54">
-        <v>-9.450148433186319</v>
+        <v>-7.347106990128174</v>
       </c>
       <c r="F54">
-        <v>-3.873725282552739</v>
+        <v>-3.978791262086815</v>
       </c>
       <c r="G54">
-        <v>-3.284039151806577</v>
+        <v>-2.924305341872751</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.188409177787022</v>
       </c>
       <c r="E55">
-        <v>-10.90493882204645</v>
+        <v>-7.111119152640456</v>
       </c>
       <c r="F55">
-        <v>-3.776208215160376</v>
+        <v>-4.130640947428797</v>
       </c>
       <c r="G55">
-        <v>-3.513877086416018</v>
+        <v>-3.505296152378227</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.05673072698645</v>
       </c>
       <c r="E56">
-        <v>-8.523808318651279</v>
+        <v>-6.83279008318102</v>
       </c>
       <c r="F56">
-        <v>-3.784891162276521</v>
+        <v>-4.356873883705163</v>
       </c>
       <c r="G56">
-        <v>-3.675885253471332</v>
+        <v>-3.285442823115228</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.914111596072676</v>
       </c>
       <c r="E57">
-        <v>-9.77667405150939</v>
+        <v>-6.761303592495937</v>
       </c>
       <c r="F57">
-        <v>-4.022327767675749</v>
+        <v>-4.454477101307416</v>
       </c>
       <c r="G57">
-        <v>-4.104869054995632</v>
+        <v>-3.265976815344313</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.701878411878775</v>
       </c>
       <c r="E58">
-        <v>-8.922508755708598</v>
+        <v>-6.298027116089236</v>
       </c>
       <c r="F58">
-        <v>-3.590282808336833</v>
+        <v>-4.526583998618905</v>
       </c>
       <c r="G58">
-        <v>-4.251562638386277</v>
+        <v>-3.317522009390765</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.373118353758652</v>
       </c>
       <c r="E59">
-        <v>-8.789031984332516</v>
+        <v>-6.813987859101173</v>
       </c>
       <c r="F59">
-        <v>-3.765359915653314</v>
+        <v>-4.472018609429099</v>
       </c>
       <c r="G59">
-        <v>-4.633798226350528</v>
+        <v>-3.113387150348225</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.896733269799095</v>
       </c>
       <c r="E60">
-        <v>-7.961666197709119</v>
+        <v>-6.213670702274353</v>
       </c>
       <c r="F60">
-        <v>-4.235586813689467</v>
+        <v>-4.605061041257922</v>
       </c>
       <c r="G60">
-        <v>-3.72004462041967</v>
+        <v>-3.27094263365322</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.257399723420567</v>
       </c>
       <c r="E61">
-        <v>-8.294432053214759</v>
+        <v>-5.317082661969706</v>
       </c>
       <c r="F61">
-        <v>-4.481707194572242</v>
+        <v>-4.689460910826956</v>
       </c>
       <c r="G61">
-        <v>-4.611213684681621</v>
+        <v>-3.454446172895022</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.454621099329246</v>
       </c>
       <c r="E62">
-        <v>-6.543850799121613</v>
+        <v>-5.525424165640596</v>
       </c>
       <c r="F62">
-        <v>-4.072468846567203</v>
+        <v>-4.406344813367752</v>
       </c>
       <c r="G62">
-        <v>-4.18018727655959</v>
+        <v>-3.234546495994473</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.502352064714948</v>
       </c>
       <c r="E63">
-        <v>-7.15659861709949</v>
+        <v>-5.035407050218602</v>
       </c>
       <c r="F63">
-        <v>-4.161071023970638</v>
+        <v>-4.379511508088867</v>
       </c>
       <c r="G63">
-        <v>-4.569825244349652</v>
+        <v>-3.327635726013239</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.422095815918611</v>
       </c>
       <c r="E64">
-        <v>-7.41458578131647</v>
+        <v>-4.567117553085411</v>
       </c>
       <c r="F64">
-        <v>-4.121914925207708</v>
+        <v>-4.706311560534703</v>
       </c>
       <c r="G64">
-        <v>-4.162025623731148</v>
+        <v>-3.814133635191297</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.240713992783665</v>
       </c>
       <c r="E65">
-        <v>-6.557232439814279</v>
+        <v>-5.203137198988705</v>
       </c>
       <c r="F65">
-        <v>-4.394000482331234</v>
+        <v>-4.905062579855791</v>
       </c>
       <c r="G65">
-        <v>-4.637529211173288</v>
+        <v>-3.612878950767923</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.986296009250737</v>
       </c>
       <c r="E66">
-        <v>-7.729332838745591</v>
+        <v>-5.180272933723977</v>
       </c>
       <c r="F66">
-        <v>-4.286217457715976</v>
+        <v>-4.415099828447939</v>
       </c>
       <c r="G66">
-        <v>-4.814613602614442</v>
+        <v>-3.947899538251089</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.687236736582171</v>
       </c>
       <c r="E67">
-        <v>-6.177873115243719</v>
+        <v>-4.111195318467167</v>
       </c>
       <c r="F67">
-        <v>-3.953901306734898</v>
+        <v>-4.922371316737287</v>
       </c>
       <c r="G67">
-        <v>-4.563992063109456</v>
+        <v>-3.172834616596918</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.367375298416721</v>
       </c>
       <c r="E68">
-        <v>-7.202127894772607</v>
+        <v>-4.883983936350121</v>
       </c>
       <c r="F68">
-        <v>-4.30839616655853</v>
+        <v>-4.96061124115272</v>
       </c>
       <c r="G68">
-        <v>-4.479493698765099</v>
+        <v>-3.041151046681328</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.04735685219554</v>
       </c>
       <c r="E69">
-        <v>-6.187604805886202</v>
+        <v>-4.167692560186862</v>
       </c>
       <c r="F69">
-        <v>-4.614724775378981</v>
+        <v>-5.048405760338426</v>
       </c>
       <c r="G69">
-        <v>-4.46159026848872</v>
+        <v>-3.087773459510884</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.742656623637777</v>
       </c>
       <c r="E70">
-        <v>-6.804939968033848</v>
+        <v>-4.419009282190544</v>
       </c>
       <c r="F70">
-        <v>-4.569688924790981</v>
+        <v>-4.75433201887499</v>
       </c>
       <c r="G70">
-        <v>-4.678407827492208</v>
+        <v>-3.235844229845867</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.463552293308167</v>
       </c>
       <c r="E71">
-        <v>-6.062537410742362</v>
+        <v>-4.884423198328865</v>
       </c>
       <c r="F71">
-        <v>-4.18986838836156</v>
+        <v>-4.857620321962658</v>
       </c>
       <c r="G71">
-        <v>-4.002801625474362</v>
+        <v>-3.065543146214678</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.218536557920769</v>
       </c>
       <c r="E72">
-        <v>-6.623234948476075</v>
+        <v>-4.379398720045451</v>
       </c>
       <c r="F72">
-        <v>-3.85082589406975</v>
+        <v>-5.071362306172209</v>
       </c>
       <c r="G72">
-        <v>-4.34698580301023</v>
+        <v>-2.909874673867069</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.010289046033239</v>
       </c>
       <c r="E73">
-        <v>-7.0845777664815</v>
+        <v>-4.754446937360711</v>
       </c>
       <c r="F73">
-        <v>-4.20872037371447</v>
+        <v>-5.252634773294227</v>
       </c>
       <c r="G73">
-        <v>-3.998554195547477</v>
+        <v>-2.647563598062916</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.838595632252042</v>
       </c>
       <c r="E74">
-        <v>-6.939286206419404</v>
+        <v>-5.283771207169283</v>
       </c>
       <c r="F74">
-        <v>-4.649228762807789</v>
+        <v>-5.290275788077436</v>
       </c>
       <c r="G74">
-        <v>-3.685912895909785</v>
+        <v>-2.316370001223148</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.698321226881958</v>
       </c>
       <c r="E75">
-        <v>-7.041290083442179</v>
+        <v>-4.285763462988851</v>
       </c>
       <c r="F75">
-        <v>-4.258796839948507</v>
+        <v>-5.301635190272027</v>
       </c>
       <c r="G75">
-        <v>-3.62415797942022</v>
+        <v>-1.87956669113509</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.583875146568167</v>
       </c>
       <c r="E76">
-        <v>-6.842191195220945</v>
+        <v>-6.038640653403886</v>
       </c>
       <c r="F76">
-        <v>-4.874648242294604</v>
+        <v>-5.431323562486914</v>
       </c>
       <c r="G76">
-        <v>-3.830967759258491</v>
+        <v>-1.712198750851696</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.488234609026638</v>
       </c>
       <c r="E77">
-        <v>-6.811764378363407</v>
+        <v>-6.302437849772707</v>
       </c>
       <c r="F77">
-        <v>-5.086021095732149</v>
+        <v>-5.644872537091612</v>
       </c>
       <c r="G77">
-        <v>-3.243710086047175</v>
+        <v>-1.839237625375688</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.405235218806362</v>
       </c>
       <c r="E78">
-        <v>-8.199075976035244</v>
+        <v>-5.981224131460633</v>
       </c>
       <c r="F78">
-        <v>-4.890066644762912</v>
+        <v>-5.542247756293587</v>
       </c>
       <c r="G78">
-        <v>-3.83991947439668</v>
+        <v>-2.095487092297435</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.32829309242804</v>
       </c>
       <c r="E79">
-        <v>-9.75002398197425</v>
+        <v>-7.562272904128624</v>
       </c>
       <c r="F79">
-        <v>-5.273417683063064</v>
+        <v>-5.888011623691712</v>
       </c>
       <c r="G79">
-        <v>-3.037903401507303</v>
+        <v>-1.51899200263429</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.249636528006532</v>
       </c>
       <c r="E80">
-        <v>-9.294975742839487</v>
+        <v>-7.110616492025605</v>
       </c>
       <c r="F80">
-        <v>-4.941156204330571</v>
+        <v>-5.732087199095359</v>
       </c>
       <c r="G80">
-        <v>-3.390555954532627</v>
+        <v>-2.011644215969853</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.162838553065522</v>
       </c>
       <c r="E81">
-        <v>-10.10110298636691</v>
+        <v>-8.196123410982244</v>
       </c>
       <c r="F81">
-        <v>-5.050721047229251</v>
+        <v>-5.657100896691739</v>
       </c>
       <c r="G81">
-        <v>-2.618526803137968</v>
+        <v>-1.812620839239948</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.061302918017359</v>
       </c>
       <c r="E82">
-        <v>-11.16360978583859</v>
+        <v>-9.159157750401437</v>
       </c>
       <c r="F82">
-        <v>-5.122433641657007</v>
+        <v>-5.82332772667671</v>
       </c>
       <c r="G82">
-        <v>-2.251347576286323</v>
+        <v>-1.11303635588116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.94250619416019</v>
       </c>
       <c r="E83">
-        <v>-11.55616961214151</v>
+        <v>-9.759302825215967</v>
       </c>
       <c r="F83">
-        <v>-5.026500412738796</v>
+        <v>-6.30684826479299</v>
       </c>
       <c r="G83">
-        <v>-2.436364034839571</v>
+        <v>-0.8566511565923034</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.804703616906666</v>
       </c>
       <c r="E84">
-        <v>-11.98028837380389</v>
+        <v>-10.90393350081675</v>
       </c>
       <c r="F84">
-        <v>-5.239260781576029</v>
+        <v>-6.321497113944097</v>
       </c>
       <c r="G84">
-        <v>-2.541937332086929</v>
+        <v>-0.8934544913523812</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.646869101072137</v>
       </c>
       <c r="E85">
-        <v>-13.90622572689605</v>
+        <v>-11.95909511544799</v>
       </c>
       <c r="F85">
-        <v>-5.598914713584296</v>
+        <v>-6.372096280009298</v>
       </c>
       <c r="G85">
-        <v>-2.186530405172932</v>
+        <v>-1.182743202756054</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.468135407445663</v>
       </c>
       <c r="E86">
-        <v>-14.60512776286985</v>
+        <v>-12.78203658296589</v>
       </c>
       <c r="F86">
-        <v>-5.595705618265851</v>
+        <v>-6.659606038172951</v>
       </c>
       <c r="G86">
-        <v>-2.572586362689502</v>
+        <v>-0.7306915199141132</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.269602326563494</v>
       </c>
       <c r="E87">
-        <v>-15.97825617994967</v>
+        <v>-15.00162283308544</v>
       </c>
       <c r="F87">
-        <v>-5.653120591321287</v>
+        <v>-6.507029874618713</v>
       </c>
       <c r="G87">
-        <v>-2.809637976029015</v>
+        <v>-0.7046342159745097</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.057092723894105</v>
       </c>
       <c r="E88">
-        <v>-17.08146037532828</v>
+        <v>-15.47589444438277</v>
       </c>
       <c r="F88">
-        <v>-5.56746491676961</v>
+        <v>-6.828067803410676</v>
       </c>
       <c r="G88">
-        <v>-1.771944166198923</v>
+        <v>-0.5719078242140493</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.839662368421023</v>
       </c>
       <c r="E89">
-        <v>-18.43038862731111</v>
+        <v>-17.18970448953363</v>
       </c>
       <c r="F89">
-        <v>-6.191333258840002</v>
+        <v>-6.725564792620862</v>
       </c>
       <c r="G89">
-        <v>-2.813498072127806</v>
+        <v>-0.8542708743495674</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.629628660888261</v>
       </c>
       <c r="E90">
-        <v>-19.9042257778475</v>
+        <v>-18.21242411637392</v>
       </c>
       <c r="F90">
-        <v>-6.180796425476392</v>
+        <v>-6.751506360390633</v>
       </c>
       <c r="G90">
-        <v>-2.578700940300536</v>
+        <v>-0.9175254679684219</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.440299292100826</v>
       </c>
       <c r="E91">
-        <v>-23.08578670446845</v>
+        <v>-20.92858924075257</v>
       </c>
       <c r="F91">
-        <v>-6.135509579565343</v>
+        <v>-6.823029258683148</v>
       </c>
       <c r="G91">
-        <v>-2.418040165279705</v>
+        <v>-1.184951336630748</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.28935968898295</v>
       </c>
       <c r="E92">
-        <v>-24.51773094195988</v>
+        <v>-23.05980232061243</v>
       </c>
       <c r="F92">
-        <v>-6.005386314463985</v>
+        <v>-7.147776202521144</v>
       </c>
       <c r="G92">
-        <v>-2.915929661658395</v>
+        <v>-1.57436418732414</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.196280387804234</v>
       </c>
       <c r="E93">
-        <v>-25.85293338922546</v>
+        <v>-25.56522132162213</v>
       </c>
       <c r="F93">
-        <v>-6.27287029066496</v>
+        <v>-6.910526393971248</v>
       </c>
       <c r="G93">
-        <v>-3.266168826985591</v>
+        <v>-1.669304012299359</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.179853821008101</v>
       </c>
       <c r="E94">
-        <v>-28.20022260636131</v>
+        <v>-26.58870626056972</v>
       </c>
       <c r="F94">
-        <v>-6.4090543058689</v>
+        <v>-6.91020457323526</v>
       </c>
       <c r="G94">
-        <v>-3.062967541785125</v>
+        <v>-2.170404737851142</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.255999407233549</v>
       </c>
       <c r="E95">
-        <v>-29.88357866381059</v>
+        <v>-29.87285976583443</v>
       </c>
       <c r="F95">
-        <v>-6.092224069299458</v>
+        <v>-7.09694260848095</v>
       </c>
       <c r="G95">
-        <v>-4.200451125805469</v>
+        <v>-3.117240625355937</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.437277323135025</v>
       </c>
       <c r="E96">
-        <v>-32.7297177849204</v>
+        <v>-31.72605624094139</v>
       </c>
       <c r="F96">
-        <v>-6.605298271245416</v>
+        <v>-7.168012803987835</v>
       </c>
       <c r="G96">
-        <v>-4.25100646673568</v>
+        <v>-3.267711541206891</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.717240149658659</v>
       </c>
       <c r="E97">
-        <v>-35.44477116893017</v>
+        <v>-33.84651193079603</v>
       </c>
       <c r="F97">
-        <v>-6.337224497453648</v>
+        <v>-7.202271180481713</v>
       </c>
       <c r="G97">
-        <v>-4.838548846863373</v>
+        <v>-3.558764773382996</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.094530616396304</v>
       </c>
       <c r="E98">
-        <v>-38.09322654994615</v>
+        <v>-36.31155505755333</v>
       </c>
       <c r="F98">
-        <v>-6.155822805016792</v>
+        <v>-7.18689253964874</v>
       </c>
       <c r="G98">
-        <v>-5.975131962497035</v>
+        <v>-4.211326267901975</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.530718340421918</v>
       </c>
       <c r="E99">
-        <v>-40.66746929892441</v>
+        <v>-39.38475639388174</v>
       </c>
       <c r="F99">
-        <v>-7.157436623172592</v>
+        <v>-7.335582003349043</v>
       </c>
       <c r="G99">
-        <v>-4.834351075119577</v>
+        <v>-4.896413872344294</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.025605417572058</v>
       </c>
       <c r="E100">
-        <v>-42.27995473815365</v>
+        <v>-41.9264665855889</v>
       </c>
       <c r="F100">
-        <v>-6.356549066409857</v>
+        <v>-7.162115242263604</v>
       </c>
       <c r="G100">
-        <v>-6.094182490634767</v>
+        <v>-5.407886537070614</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.507897512309527</v>
       </c>
       <c r="E101">
-        <v>-45.76530381510516</v>
+        <v>-45.09790637280271</v>
       </c>
       <c r="F101">
-        <v>-6.607442086083861</v>
+        <v>-7.271741798533792</v>
       </c>
       <c r="G101">
-        <v>-5.960353687209729</v>
+        <v>-5.630149943486203</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.025131827314929</v>
       </c>
       <c r="E102">
-        <v>-48.15697207751618</v>
+        <v>-46.91170965251695</v>
       </c>
       <c r="F102">
-        <v>-6.573774335548179</v>
+        <v>-7.241551534355063</v>
       </c>
       <c r="G102">
-        <v>-6.67722583937459</v>
+        <v>-6.822380019089475</v>
       </c>
     </row>
   </sheetData>
